--- a/artfynd/A 26231-2024 artfynd.xlsx
+++ b/artfynd/A 26231-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127456643</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127456649</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127456647</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127456646</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127456645</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127456653</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127456648</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127456642</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>127456656</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>127456654</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127456651</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127456652</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 26231-2024 artfynd.xlsx
+++ b/artfynd/A 26231-2024 artfynd.xlsx
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127456653</v>
+        <v>127456648</v>
       </c>
       <c r="B7" t="n">
         <v>57661</v>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456215</v>
+        <v>456205</v>
       </c>
       <c r="R7" t="n">
-        <v>7052716</v>
+        <v>7052518</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127456648</v>
+        <v>127456653</v>
       </c>
       <c r="B8" t="n">
         <v>57661</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456205</v>
+        <v>456215</v>
       </c>
       <c r="R8" t="n">
-        <v>7052518</v>
+        <v>7052716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127456654</v>
+        <v>127456651</v>
       </c>
       <c r="B11" t="n">
         <v>57661</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456210</v>
+        <v>456220</v>
       </c>
       <c r="R11" t="n">
-        <v>7052758</v>
+        <v>7052642</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127456651</v>
+        <v>127456654</v>
       </c>
       <c r="B12" t="n">
         <v>57661</v>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456220</v>
+        <v>456210</v>
       </c>
       <c r="R12" t="n">
-        <v>7052642</v>
+        <v>7052758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 26231-2024 artfynd.xlsx
+++ b/artfynd/A 26231-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127456643</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127456649</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127456647</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127456646</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127456645</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127456648</v>
+        <v>127456653</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456205</v>
+        <v>456215</v>
       </c>
       <c r="R7" t="n">
-        <v>7052518</v>
+        <v>7052716</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127456653</v>
+        <v>127456648</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456215</v>
+        <v>456205</v>
       </c>
       <c r="R8" t="n">
-        <v>7052716</v>
+        <v>7052518</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
         <v>127456642</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>127456656</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127456651</v>
+        <v>127456654</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456220</v>
+        <v>456210</v>
       </c>
       <c r="R11" t="n">
-        <v>7052642</v>
+        <v>7052758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127456654</v>
+        <v>127456651</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456210</v>
+        <v>456220</v>
       </c>
       <c r="R12" t="n">
-        <v>7052758</v>
+        <v>7052642</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
         <v>127456652</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 26231-2024 artfynd.xlsx
+++ b/artfynd/A 26231-2024 artfynd.xlsx
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127456653</v>
+        <v>127456648</v>
       </c>
       <c r="B7" t="n">
         <v>57663</v>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456215</v>
+        <v>456205</v>
       </c>
       <c r="R7" t="n">
-        <v>7052716</v>
+        <v>7052518</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127456648</v>
+        <v>127456653</v>
       </c>
       <c r="B8" t="n">
         <v>57663</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456205</v>
+        <v>456215</v>
       </c>
       <c r="R8" t="n">
-        <v>7052518</v>
+        <v>7052716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127456656</v>
+        <v>127456651</v>
       </c>
       <c r="B10" t="n">
         <v>57663</v>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456216</v>
+        <v>456220</v>
       </c>
       <c r="R10" t="n">
-        <v>7052759</v>
+        <v>7052642</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127456651</v>
+        <v>127456656</v>
       </c>
       <c r="B12" t="n">
         <v>57663</v>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456220</v>
+        <v>456216</v>
       </c>
       <c r="R12" t="n">
-        <v>7052642</v>
+        <v>7052759</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 26231-2024 artfynd.xlsx
+++ b/artfynd/A 26231-2024 artfynd.xlsx
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127456646</v>
+        <v>127456645</v>
       </c>
       <c r="B5" t="n">
         <v>57663</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456244</v>
+        <v>456292</v>
       </c>
       <c r="R5" t="n">
-        <v>7052549</v>
+        <v>7052625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127456645</v>
+        <v>127456646</v>
       </c>
       <c r="B6" t="n">
         <v>57663</v>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456292</v>
+        <v>456244</v>
       </c>
       <c r="R6" t="n">
-        <v>7052625</v>
+        <v>7052549</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127456648</v>
+        <v>127456653</v>
       </c>
       <c r="B7" t="n">
         <v>57663</v>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456205</v>
+        <v>456215</v>
       </c>
       <c r="R7" t="n">
-        <v>7052518</v>
+        <v>7052716</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127456653</v>
+        <v>127456648</v>
       </c>
       <c r="B8" t="n">
         <v>57663</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456215</v>
+        <v>456205</v>
       </c>
       <c r="R8" t="n">
-        <v>7052716</v>
+        <v>7052518</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 26231-2024 artfynd.xlsx
+++ b/artfynd/A 26231-2024 artfynd.xlsx
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127456645</v>
+        <v>127456646</v>
       </c>
       <c r="B5" t="n">
         <v>57663</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456292</v>
+        <v>456244</v>
       </c>
       <c r="R5" t="n">
-        <v>7052625</v>
+        <v>7052549</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127456646</v>
+        <v>127456645</v>
       </c>
       <c r="B6" t="n">
         <v>57663</v>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456244</v>
+        <v>456292</v>
       </c>
       <c r="R6" t="n">
-        <v>7052549</v>
+        <v>7052625</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127456651</v>
+        <v>127456656</v>
       </c>
       <c r="B10" t="n">
         <v>57663</v>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456220</v>
+        <v>456216</v>
       </c>
       <c r="R10" t="n">
-        <v>7052642</v>
+        <v>7052759</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127456656</v>
+        <v>127456651</v>
       </c>
       <c r="B12" t="n">
         <v>57663</v>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456216</v>
+        <v>456220</v>
       </c>
       <c r="R12" t="n">
-        <v>7052759</v>
+        <v>7052642</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 26231-2024 artfynd.xlsx
+++ b/artfynd/A 26231-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127456643</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127456649</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127456647</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127456646</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127456645</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127456653</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127456648</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127456642</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127456656</v>
+        <v>127456651</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456216</v>
+        <v>456220</v>
       </c>
       <c r="R10" t="n">
-        <v>7052759</v>
+        <v>7052642</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127456654</v>
+        <v>127456656</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456210</v>
+        <v>456216</v>
       </c>
       <c r="R11" t="n">
-        <v>7052758</v>
+        <v>7052759</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127456651</v>
+        <v>127456654</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456220</v>
+        <v>456210</v>
       </c>
       <c r="R12" t="n">
-        <v>7052642</v>
+        <v>7052758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
         <v>127456652</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 26231-2024 artfynd.xlsx
+++ b/artfynd/A 26231-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127456643</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127456649</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127456647</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127456646</v>
+        <v>127456645</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456244</v>
+        <v>456292</v>
       </c>
       <c r="R5" t="n">
-        <v>7052549</v>
+        <v>7052625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127456645</v>
+        <v>127456646</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456292</v>
+        <v>456244</v>
       </c>
       <c r="R6" t="n">
-        <v>7052625</v>
+        <v>7052549</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127456653</v>
+        <v>127456648</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456215</v>
+        <v>456205</v>
       </c>
       <c r="R7" t="n">
-        <v>7052716</v>
+        <v>7052518</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127456648</v>
+        <v>127456653</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456205</v>
+        <v>456215</v>
       </c>
       <c r="R8" t="n">
-        <v>7052518</v>
+        <v>7052716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
         <v>127456642</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>127456651</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>127456656</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127456654</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127456652</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 26231-2024 artfynd.xlsx
+++ b/artfynd/A 26231-2024 artfynd.xlsx
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127456645</v>
+        <v>127456646</v>
       </c>
       <c r="B5" t="n">
         <v>57672</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456292</v>
+        <v>456244</v>
       </c>
       <c r="R5" t="n">
-        <v>7052625</v>
+        <v>7052549</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127456646</v>
+        <v>127456645</v>
       </c>
       <c r="B6" t="n">
         <v>57672</v>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456244</v>
+        <v>456292</v>
       </c>
       <c r="R6" t="n">
-        <v>7052549</v>
+        <v>7052625</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127456648</v>
+        <v>127456653</v>
       </c>
       <c r="B7" t="n">
         <v>57672</v>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456205</v>
+        <v>456215</v>
       </c>
       <c r="R7" t="n">
-        <v>7052518</v>
+        <v>7052716</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127456653</v>
+        <v>127456648</v>
       </c>
       <c r="B8" t="n">
         <v>57672</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456215</v>
+        <v>456205</v>
       </c>
       <c r="R8" t="n">
-        <v>7052716</v>
+        <v>7052518</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127456651</v>
+        <v>127456656</v>
       </c>
       <c r="B10" t="n">
         <v>57672</v>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456220</v>
+        <v>456216</v>
       </c>
       <c r="R10" t="n">
-        <v>7052642</v>
+        <v>7052759</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127456656</v>
+        <v>127456654</v>
       </c>
       <c r="B11" t="n">
         <v>57672</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456216</v>
+        <v>456210</v>
       </c>
       <c r="R11" t="n">
-        <v>7052759</v>
+        <v>7052758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127456654</v>
+        <v>127456651</v>
       </c>
       <c r="B12" t="n">
         <v>57672</v>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456210</v>
+        <v>456220</v>
       </c>
       <c r="R12" t="n">
-        <v>7052758</v>
+        <v>7052642</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 26231-2024 artfynd.xlsx
+++ b/artfynd/A 26231-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127456643</v>
+        <v>127456642</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456392</v>
+        <v>456407</v>
       </c>
       <c r="R2" t="n">
-        <v>7052546</v>
+        <v>7052529</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127456649</v>
+        <v>127456643</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456234</v>
+        <v>456392</v>
       </c>
       <c r="R3" t="n">
-        <v>7052618</v>
+        <v>7052546</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127456647</v>
+        <v>127456645</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456240</v>
+        <v>456292</v>
       </c>
       <c r="R4" t="n">
-        <v>7052547</v>
+        <v>7052625</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>127456646</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127456645</v>
+        <v>127456647</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456292</v>
+        <v>456240</v>
       </c>
       <c r="R6" t="n">
-        <v>7052625</v>
+        <v>7052547</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127456653</v>
+        <v>127456648</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456215</v>
+        <v>456205</v>
       </c>
       <c r="R7" t="n">
-        <v>7052716</v>
+        <v>7052518</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127456648</v>
+        <v>127456649</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456205</v>
+        <v>456234</v>
       </c>
       <c r="R8" t="n">
-        <v>7052518</v>
+        <v>7052618</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127456642</v>
+        <v>127456651</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456407</v>
+        <v>456220</v>
       </c>
       <c r="R9" t="n">
-        <v>7052529</v>
+        <v>7052642</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127456656</v>
+        <v>127456652</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456216</v>
+        <v>456211</v>
       </c>
       <c r="R10" t="n">
-        <v>7052759</v>
+        <v>7052681</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127456654</v>
+        <v>127456653</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456210</v>
+        <v>456215</v>
       </c>
       <c r="R11" t="n">
-        <v>7052758</v>
+        <v>7052716</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127456651</v>
+        <v>127456654</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456220</v>
+        <v>456210</v>
       </c>
       <c r="R12" t="n">
-        <v>7052642</v>
+        <v>7052758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127456652</v>
+        <v>127456656</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456211</v>
+        <v>456216</v>
       </c>
       <c r="R13" t="n">
-        <v>7052681</v>
+        <v>7052759</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 26231-2024 artfynd.xlsx
+++ b/artfynd/A 26231-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456642</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456643</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456645</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456646</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456647</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456648</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456649</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456651</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456652</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456653</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456654</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,8 +1956,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456656</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>